--- a/kawasaki_project/川崎町_サービス見込量・給付費推計ワークブック.xlsx
+++ b/kawasaki_project/川崎町_サービス見込量・給付費推計ワークブック.xlsx
@@ -235,6 +235,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -254,9 +257,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1399,14 +1399,14 @@
           <t>第1号被保険者数（人）</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>3262</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>3234</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>3206</v>
+      <c r="B5" s="16" t="n">
+        <v>3187</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>3160</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>3133</v>
       </c>
       <c r="E5" s="14">
         <f>SUM(B5:D5)</f>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>保険料試算ワークブック 01!B8:B10と同値</t>
+          <t>第9期計画の推計をR7年度末実績3,240人（同計画推計比−2.29%）で補正した値</t>
         </is>
       </c>
     </row>
@@ -1424,23 +1424,23 @@
           <t>認定率</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>0.183</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="B6" s="17" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>【入力】</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>R8実績見込18.1%からの上昇を見込む。年齢階級別認定率が入手できれば置換</t>
+          <t>R7年度末実績17.31%（561人÷3,240人）からの上昇。年齢階級別認定率は65-74歳3.87%／75-84歳13.22%／85歳以上58.67%</t>
         </is>
       </c>
     </row>
@@ -1450,19 +1450,19 @@
           <t>認定者数（人）</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>ROUND(B5*B6,0)</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>ROUND(C5*C6,0)</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>ROUND(D5*D6,0)</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>SUM(B7:D7)</f>
         <v/>
       </c>
@@ -1522,7 +1522,7 @@
           <t>要支援1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>0.057</v>
       </c>
       <c r="C11" s="9">
@@ -1549,7 +1549,7 @@
           <t>要支援2</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0.158</v>
       </c>
       <c r="C12" s="9">
@@ -1576,7 +1576,7 @@
           <t>要介護1</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>0.104</v>
       </c>
       <c r="C13" s="9">
@@ -1603,7 +1603,7 @@
           <t>要介護2</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>0.241</v>
       </c>
       <c r="C14" s="9">
@@ -1630,7 +1630,7 @@
           <t>要介護3</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>0.152</v>
       </c>
       <c r="C15" s="9">
@@ -1657,7 +1657,7 @@
           <t>要介護4</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>0.177</v>
       </c>
       <c r="C16" s="9">
@@ -1684,7 +1684,7 @@
           <t>要介護5</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>0.111</v>
       </c>
       <c r="C17" s="9">
@@ -1711,7 +1711,7 @@
           <t>計</t>
         </is>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <f>SUM(B11:B17)</f>
         <v/>
       </c>
@@ -1824,7 +1824,7 @@
       <c r="D5" s="11" t="n">
         <v>0.4834782608695652</v>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="21" t="n">
         <v>0.4834782608695652</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -1848,7 +1848,7 @@
       <c r="D6" s="11" t="n">
         <v>0.08</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="21" t="n">
         <v>0.08</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -1872,7 +1872,7 @@
       <c r="D7" s="11" t="n">
         <v>0.2278260869565217</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="21" t="n">
         <v>0.2278260869565217</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -1887,19 +1887,19 @@
           <t>受給率（合計）</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <f>SUM(C5:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
@@ -2003,19 +2003,19 @@
           <t>居宅サービス</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="22" t="n">
         <v>108.9540332147094</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="22" t="n">
         <v>109.3318399044206</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="22" t="n">
         <v>101.7604916067146</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="23">
         <f>D5*E5</f>
         <v/>
       </c>
@@ -2026,19 +2026,19 @@
           <t>地域密着型サービス</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="22" t="n">
         <v>270.5706521739131</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="22" t="n">
         <v>270.8581560283688</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="22" t="n">
         <v>277.4311594202899</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="23">
         <f>D6*E6</f>
         <v/>
       </c>
@@ -2049,19 +2049,19 @@
           <t>施設サービス</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="22" t="n">
         <v>284.0314102564103</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="22" t="n">
         <v>296.825940860215</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="22" t="n">
         <v>298.4611959287532</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="23">
         <f>D7*E7</f>
         <v/>
       </c>
@@ -2407,19 +2407,19 @@
           <t>総給付額 計</t>
         </is>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="19">
         <f>SUM(B13:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="19">
         <f>SUM(C13:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="19">
         <f>SUM(D13:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="19">
         <f>SUM(E13:E15)</f>
         <v/>
       </c>
@@ -2430,13 +2430,13 @@
           <t>補完項目</t>
         </is>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" s="16" t="n">
         <v>88451</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="16" t="n">
         <v>89512</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="16" t="n">
         <v>90586</v>
       </c>
       <c r="E17" s="9">
@@ -2455,19 +2455,19 @@
           <t>標準給付費見込額</t>
         </is>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="19">
         <f>B16+B17</f>
         <v/>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="19">
         <f>C16+C17</f>
         <v/>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="19">
         <f>D16+D17</f>
         <v/>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="19">
         <f>E16+E17</f>
         <v/>
       </c>
@@ -2565,7 +2565,7 @@
           <t>① 現状維持（利用率据置）</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="9">
@@ -2576,7 +2576,7 @@
         <f>'05_見込量・給付費'!E18+B5*'04_単価の設定'!$F$7*12*3</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>ROUND((D5*(1+'07_保険料への反映'!$B$8)*0.23+D5*'07_保険料への反映'!$B$9-D5*'07_保険料への反映'!$B$10-'07_保険料への反映'!$B$11)*1000/('07_保険料への反映'!$B$12*12*'07_保険料への反映'!$B$13*'07_保険料への反映'!$B$14),0)</f>
         <v/>
       </c>
@@ -2592,7 +2592,7 @@
           <t>② 一部反映（申込の2割）</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C6" s="9">
@@ -2603,7 +2603,7 @@
         <f>'05_見込量・給付費'!E18+B6*'04_単価の設定'!$F$7*12*3</f>
         <v/>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>ROUND((D6*(1+'07_保険料への反映'!$B$8)*0.23+D6*'07_保険料への反映'!$B$9-D6*'07_保険料への反映'!$B$10-'07_保険料への反映'!$B$11)*1000/('07_保険料への反映'!$B$12*12*'07_保険料への反映'!$B$13*'07_保険料への反映'!$B$14),0)</f>
         <v/>
       </c>
@@ -2619,7 +2619,7 @@
           <t>③ 相当程度の反映（申込の4割）</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="16" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="9">
@@ -2630,7 +2630,7 @@
         <f>'05_見込量・給付費'!E18+B7*'04_単価の設定'!$F$7*12*3</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>ROUND((D7*(1+'07_保険料への反映'!$B$8)*0.23+D7*'07_保険料への反映'!$B$9-D7*'07_保険料への反映'!$B$10-'07_保険料への反映'!$B$11)*1000/('07_保険料への反映'!$B$12*12*'07_保険料への反映'!$B$13*'07_保険料への反映'!$B$14),0)</f>
         <v/>
       </c>
@@ -2646,7 +2646,7 @@
           <t>④ 大幅反映（申込の6割）</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="16" t="n">
         <v>30</v>
       </c>
       <c r="C8" s="9">
@@ -2657,7 +2657,7 @@
         <f>'05_見込量・給付費'!E18+B8*'04_単価の設定'!$F$7*12*3</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>ROUND((D8*(1+'07_保険料への反映'!$B$8)*0.23+D8*'07_保険料への反映'!$B$9-D8*'07_保険料への反映'!$B$10-'07_保険料への反映'!$B$11)*1000/('07_保険料への反映'!$B$12*12*'07_保険料への反映'!$B$13*'07_保険料への反映'!$B$14),0)</f>
         <v/>
       </c>
@@ -2761,7 +2761,7 @@
           <t>標準給付費（3年計・千円）</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>'05_見込量・給付費'!E18</f>
         <v/>
       </c>
@@ -2792,7 +2792,7 @@
           <t>調整交付金相当額率</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="21" t="n">
         <v>0.05</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -2807,12 +2807,12 @@
           <t>調整交付金見込率</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.039</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>第9期実績3.9%。標準5%との乖離は要確認</t>
+          <t>第9期実績3.9%。標準5%との乖離は要確認（R7年度の交付実績で確定）</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
           <t>第1号被保険者数 3年計（人）</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <f>'02_認定者数の推計'!E5</f>
         <v/>
       </c>
@@ -2853,12 +2853,12 @@
           <t>予定収納率</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
-        <v>0.96</v>
+      <c r="B12" s="21" t="n">
+        <v>0.967</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>第9期と同水準（暫定）</t>
+          <t>R7年度実績の総合収納率（様式3：244,747,850÷253,091,271）</t>
         </is>
       </c>
     </row>
@@ -2869,11 +2869,11 @@
         </is>
       </c>
       <c r="B13" s="26" t="n">
-        <v>0.9734</v>
+        <v>1.0137</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>R3年度末の所得段階別人数×第9期軽減前料率で算定（実績データ確認サマリー04シート）</t>
+          <t>R7年度末の所得段階別被保険者数（13段階・3,240人）×保険者の定める割合で実算定（年報 様式1）</t>
         </is>
       </c>
     </row>
@@ -2923,18 +2923,18 @@
           <t>基金取崩額（千円）</t>
         </is>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="23" t="n">
-        <v>26850</v>
-      </c>
-      <c r="D17" s="23" t="n">
-        <v>53700</v>
+      <c r="C17" s="16" t="n">
+        <v>39154</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>78308</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>取崩なし／50%／全額（残高53,700千円）</t>
+          <t>取崩なし／50%／全額（残高78,308千円＝131,700−第9期取崩予算53,392）</t>
         </is>
       </c>
     </row>
